--- a/ARG_USD_Sovereign_Curve_Template.xlsx
+++ b/ARG_USD_Sovereign_Curve_Template.xlsx
@@ -832,7 +832,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10. Rich_Cheap_Rank — 8-signal composite z-score with editable weights (Settings!C42:C49).</t>
+          <t>10. Rich_Cheap_Rank — 5-signal composite z-score (curve residual + 12M C+R + DTS-adj carry + YTM + liquidity). Weights editable on Settings!C42:C46. Missing-data robust: any signal that errors out is dropped from BOTH numerator and denominator, so the composite always returns a real number based on whatever signals are available. Peer/EMBI/percentile tabs still exist as standalone diagnostics — they just don't feed the headline score.</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10049,13 +10049,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -10101,40 +10098,25 @@
       </c>
       <c r="I1" s="21" t="inlineStr">
         <is>
-          <t>Spread vs peer</t>
+          <t>Liq score</t>
         </is>
       </c>
       <c r="J1" s="21" t="inlineStr">
         <is>
-          <t>Spread vs EMBI</t>
+          <t>Liquid?</t>
         </is>
       </c>
       <c r="K1" s="21" t="inlineStr">
         <is>
-          <t>1Y Spr Pctile</t>
+          <t>Composite z</t>
         </is>
       </c>
       <c r="L1" s="21" t="inlineStr">
         <is>
-          <t>Liq score</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="M1" s="21" t="inlineStr">
-        <is>
-          <t>Liquid?</t>
-        </is>
-      </c>
-      <c r="N1" s="21" t="inlineStr">
-        <is>
-          <t>Composite z</t>
-        </is>
-      </c>
-      <c r="O1" s="21" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="P1" s="21" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
@@ -10154,13 +10136,10 @@
       <c r="K2" s="30" t="inlineStr"/>
       <c r="L2" s="30" t="inlineStr"/>
       <c r="M2" s="30" t="inlineStr"/>
-      <c r="N2" s="30" t="inlineStr"/>
-      <c r="O2" s="30" t="inlineStr"/>
-      <c r="P2" s="30" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="10">
-        <f>IF(N3="","",RANK(N3,$N$3:$N$27))</f>
+        <f>IF(K3="","",RANK(K3,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B3" s="25">
@@ -10191,42 +10170,30 @@
         <f>IFERROR(Bonds_Live!K3,"")</f>
         <v/>
       </c>
-      <c r="I3" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H24,"")</f>
-        <v/>
-      </c>
-      <c r="J3" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I24,"")</f>
-        <v/>
-      </c>
-      <c r="K3" s="36">
-        <f>IFERROR(Spread_History!H3,"")</f>
-        <v/>
-      </c>
-      <c r="L3" s="34">
+      <c r="I3" s="34">
         <f>IFERROR(Liquidity_Gate!I3,"")</f>
         <v/>
       </c>
-      <c r="M3" s="25">
+      <c r="J3" s="25">
         <f>IFERROR(Liquidity_Gate!J3,"")</f>
         <v/>
       </c>
-      <c r="N3" s="16">
-        <f>IFERROR(Settings!$C$42*((E3-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F3-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G3-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H3-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I3-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J3-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K3-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L3-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="10">
-        <f>IFERROR(IF(N3="","",IF(N3&gt;1,"STRONG BUY",IF(N3&gt;0.3,"BUY",IF(N3&gt;-0.3,"HOLD",IF(N3&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="10">
-        <f>IFERROR(IF(N3="","",IF(M3&lt;&gt;"PASS","SKIP — illiquid",O3)),"")</f>
+      <c r="K3" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E3),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F3),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G3),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H3),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I3),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E3-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F3-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G3-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H3-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I3-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E3),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F3),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G3),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H3),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I3),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="10">
+        <f>IFERROR(IF(K3="","",IF(K3&gt;1,"STRONG BUY",IF(K3&gt;0.3,"BUY",IF(K3&gt;-0.3,"HOLD",IF(K3&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="10">
+        <f>IFERROR(IF(K3="","",IF(J3&lt;&gt;"PASS","SKIP — illiquid",L3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>IF(N4="","",RANK(N4,$N$3:$N$27))</f>
+        <f>IF(K4="","",RANK(K4,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B4" s="25">
@@ -10257,42 +10224,30 @@
         <f>IFERROR(Bonds_Live!K4,"")</f>
         <v/>
       </c>
-      <c r="I4" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H25,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I25,"")</f>
-        <v/>
-      </c>
-      <c r="K4" s="36">
-        <f>IFERROR(Spread_History!H4,"")</f>
-        <v/>
-      </c>
-      <c r="L4" s="34">
+      <c r="I4" s="34">
         <f>IFERROR(Liquidity_Gate!I4,"")</f>
         <v/>
       </c>
-      <c r="M4" s="25">
+      <c r="J4" s="25">
         <f>IFERROR(Liquidity_Gate!J4,"")</f>
         <v/>
       </c>
-      <c r="N4" s="16">
-        <f>IFERROR(Settings!$C$42*((E4-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F4-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G4-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H4-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I4-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J4-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K4-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L4-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O4" s="10">
-        <f>IFERROR(IF(N4="","",IF(N4&gt;1,"STRONG BUY",IF(N4&gt;0.3,"BUY",IF(N4&gt;-0.3,"HOLD",IF(N4&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P4" s="10">
-        <f>IFERROR(IF(N4="","",IF(M4&lt;&gt;"PASS","SKIP — illiquid",O4)),"")</f>
+      <c r="K4" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E4),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F4),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G4),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H4),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I4),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E4-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F4-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G4-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H4-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I4-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E4),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F4),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G4),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H4),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I4),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="10">
+        <f>IFERROR(IF(K4="","",IF(K4&gt;1,"STRONG BUY",IF(K4&gt;0.3,"BUY",IF(K4&gt;-0.3,"HOLD",IF(K4&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="10">
+        <f>IFERROR(IF(K4="","",IF(J4&lt;&gt;"PASS","SKIP — illiquid",L4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10">
-        <f>IF(N5="","",RANK(N5,$N$3:$N$27))</f>
+        <f>IF(K5="","",RANK(K5,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B5" s="25">
@@ -10323,42 +10278,30 @@
         <f>IFERROR(Bonds_Live!K5,"")</f>
         <v/>
       </c>
-      <c r="I5" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H26,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I26,"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="36">
-        <f>IFERROR(Spread_History!H5,"")</f>
-        <v/>
-      </c>
-      <c r="L5" s="34">
+      <c r="I5" s="34">
         <f>IFERROR(Liquidity_Gate!I5,"")</f>
         <v/>
       </c>
-      <c r="M5" s="25">
+      <c r="J5" s="25">
         <f>IFERROR(Liquidity_Gate!J5,"")</f>
         <v/>
       </c>
-      <c r="N5" s="16">
-        <f>IFERROR(Settings!$C$42*((E5-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F5-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G5-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H5-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I5-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J5-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K5-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L5-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="10">
-        <f>IFERROR(IF(N5="","",IF(N5&gt;1,"STRONG BUY",IF(N5&gt;0.3,"BUY",IF(N5&gt;-0.3,"HOLD",IF(N5&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P5" s="10">
-        <f>IFERROR(IF(N5="","",IF(M5&lt;&gt;"PASS","SKIP — illiquid",O5)),"")</f>
+      <c r="K5" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E5),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F5),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G5),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H5),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I5),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E5-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F5-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G5-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H5-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I5-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E5),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F5),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G5),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H5),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I5),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="10">
+        <f>IFERROR(IF(K5="","",IF(K5&gt;1,"STRONG BUY",IF(K5&gt;0.3,"BUY",IF(K5&gt;-0.3,"HOLD",IF(K5&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="10">
+        <f>IFERROR(IF(K5="","",IF(J5&lt;&gt;"PASS","SKIP — illiquid",L5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10">
-        <f>IF(N6="","",RANK(N6,$N$3:$N$27))</f>
+        <f>IF(K6="","",RANK(K6,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B6" s="25">
@@ -10389,42 +10332,30 @@
         <f>IFERROR(Bonds_Live!K6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H27,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I27,"")</f>
-        <v/>
-      </c>
-      <c r="K6" s="36">
-        <f>IFERROR(Spread_History!H6,"")</f>
-        <v/>
-      </c>
-      <c r="L6" s="34">
+      <c r="I6" s="34">
         <f>IFERROR(Liquidity_Gate!I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="25">
+      <c r="J6" s="25">
         <f>IFERROR(Liquidity_Gate!J6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="16">
-        <f>IFERROR(Settings!$C$42*((E6-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F6-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G6-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H6-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I6-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J6-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K6-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L6-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O6" s="10">
-        <f>IFERROR(IF(N6="","",IF(N6&gt;1,"STRONG BUY",IF(N6&gt;0.3,"BUY",IF(N6&gt;-0.3,"HOLD",IF(N6&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P6" s="10">
-        <f>IFERROR(IF(N6="","",IF(M6&lt;&gt;"PASS","SKIP — illiquid",O6)),"")</f>
+      <c r="K6" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E6),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F6),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G6),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H6),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I6),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E6-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F6-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G6-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H6-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I6-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E6),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F6),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G6),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H6),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I6),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="10">
+        <f>IFERROR(IF(K6="","",IF(K6&gt;1,"STRONG BUY",IF(K6&gt;0.3,"BUY",IF(K6&gt;-0.3,"HOLD",IF(K6&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="10">
+        <f>IFERROR(IF(K6="","",IF(J6&lt;&gt;"PASS","SKIP — illiquid",L6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10">
-        <f>IF(N7="","",RANK(N7,$N$3:$N$27))</f>
+        <f>IF(K7="","",RANK(K7,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B7" s="25">
@@ -10455,42 +10386,30 @@
         <f>IFERROR(Bonds_Live!K7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H28,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I28,"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="36">
-        <f>IFERROR(Spread_History!H7,"")</f>
-        <v/>
-      </c>
-      <c r="L7" s="34">
+      <c r="I7" s="34">
         <f>IFERROR(Liquidity_Gate!I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="25">
+      <c r="J7" s="25">
         <f>IFERROR(Liquidity_Gate!J7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="16">
-        <f>IFERROR(Settings!$C$42*((E7-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F7-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G7-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H7-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I7-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J7-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K7-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L7-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O7" s="10">
-        <f>IFERROR(IF(N7="","",IF(N7&gt;1,"STRONG BUY",IF(N7&gt;0.3,"BUY",IF(N7&gt;-0.3,"HOLD",IF(N7&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P7" s="10">
-        <f>IFERROR(IF(N7="","",IF(M7&lt;&gt;"PASS","SKIP — illiquid",O7)),"")</f>
+      <c r="K7" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E7),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F7),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G7),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H7),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I7),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E7-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F7-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G7-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H7-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I7-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E7),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F7),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G7),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H7),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I7),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="10">
+        <f>IFERROR(IF(K7="","",IF(K7&gt;1,"STRONG BUY",IF(K7&gt;0.3,"BUY",IF(K7&gt;-0.3,"HOLD",IF(K7&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="10">
+        <f>IFERROR(IF(K7="","",IF(J7&lt;&gt;"PASS","SKIP — illiquid",L7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10">
-        <f>IF(N8="","",RANK(N8,$N$3:$N$27))</f>
+        <f>IF(K8="","",RANK(K8,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B8" s="25">
@@ -10521,42 +10440,30 @@
         <f>IFERROR(Bonds_Live!K8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H29,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I29,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="36">
-        <f>IFERROR(Spread_History!H8,"")</f>
-        <v/>
-      </c>
-      <c r="L8" s="34">
+      <c r="I8" s="34">
         <f>IFERROR(Liquidity_Gate!I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="25">
+      <c r="J8" s="25">
         <f>IFERROR(Liquidity_Gate!J8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="16">
-        <f>IFERROR(Settings!$C$42*((E8-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F8-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G8-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H8-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I8-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J8-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K8-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L8-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O8" s="10">
-        <f>IFERROR(IF(N8="","",IF(N8&gt;1,"STRONG BUY",IF(N8&gt;0.3,"BUY",IF(N8&gt;-0.3,"HOLD",IF(N8&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P8" s="10">
-        <f>IFERROR(IF(N8="","",IF(M8&lt;&gt;"PASS","SKIP — illiquid",O8)),"")</f>
+      <c r="K8" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E8),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F8),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G8),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H8),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I8),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E8-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F8-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G8-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H8-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I8-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E8),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F8),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G8),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H8),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I8),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="10">
+        <f>IFERROR(IF(K8="","",IF(K8&gt;1,"STRONG BUY",IF(K8&gt;0.3,"BUY",IF(K8&gt;-0.3,"HOLD",IF(K8&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="10">
+        <f>IFERROR(IF(K8="","",IF(J8&lt;&gt;"PASS","SKIP — illiquid",L8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10">
-        <f>IF(N9="","",RANK(N9,$N$3:$N$27))</f>
+        <f>IF(K9="","",RANK(K9,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B9" s="25">
@@ -10587,42 +10494,30 @@
         <f>IFERROR(Bonds_Live!K9,"")</f>
         <v/>
       </c>
-      <c r="I9" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H30,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I30,"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="36">
-        <f>IFERROR(Spread_History!H9,"")</f>
-        <v/>
-      </c>
-      <c r="L9" s="34">
+      <c r="I9" s="34">
         <f>IFERROR(Liquidity_Gate!I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="25">
+      <c r="J9" s="25">
         <f>IFERROR(Liquidity_Gate!J9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="16">
-        <f>IFERROR(Settings!$C$42*((E9-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F9-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G9-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H9-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I9-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J9-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K9-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L9-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O9" s="10">
-        <f>IFERROR(IF(N9="","",IF(N9&gt;1,"STRONG BUY",IF(N9&gt;0.3,"BUY",IF(N9&gt;-0.3,"HOLD",IF(N9&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P9" s="10">
-        <f>IFERROR(IF(N9="","",IF(M9&lt;&gt;"PASS","SKIP — illiquid",O9)),"")</f>
+      <c r="K9" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E9),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F9),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G9),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H9),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I9),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E9-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F9-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G9-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H9-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I9-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E9),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F9),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G9),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H9),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I9),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="10">
+        <f>IFERROR(IF(K9="","",IF(K9&gt;1,"STRONG BUY",IF(K9&gt;0.3,"BUY",IF(K9&gt;-0.3,"HOLD",IF(K9&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="10">
+        <f>IFERROR(IF(K9="","",IF(J9&lt;&gt;"PASS","SKIP — illiquid",L9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10">
-        <f>IF(N10="","",RANK(N10,$N$3:$N$27))</f>
+        <f>IF(K10="","",RANK(K10,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B10" s="25">
@@ -10653,42 +10548,30 @@
         <f>IFERROR(Bonds_Live!K10,"")</f>
         <v/>
       </c>
-      <c r="I10" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H31,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I31,"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="36">
-        <f>IFERROR(Spread_History!H10,"")</f>
-        <v/>
-      </c>
-      <c r="L10" s="34">
+      <c r="I10" s="34">
         <f>IFERROR(Liquidity_Gate!I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="25">
+      <c r="J10" s="25">
         <f>IFERROR(Liquidity_Gate!J10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="16">
-        <f>IFERROR(Settings!$C$42*((E10-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F10-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G10-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H10-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I10-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J10-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K10-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L10-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O10" s="10">
-        <f>IFERROR(IF(N10="","",IF(N10&gt;1,"STRONG BUY",IF(N10&gt;0.3,"BUY",IF(N10&gt;-0.3,"HOLD",IF(N10&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="10">
-        <f>IFERROR(IF(N10="","",IF(M10&lt;&gt;"PASS","SKIP — illiquid",O10)),"")</f>
+      <c r="K10" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E10),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F10),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G10),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H10),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I10),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E10-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F10-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G10-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H10-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I10-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E10),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F10),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G10),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H10),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I10),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="10">
+        <f>IFERROR(IF(K10="","",IF(K10&gt;1,"STRONG BUY",IF(K10&gt;0.3,"BUY",IF(K10&gt;-0.3,"HOLD",IF(K10&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="10">
+        <f>IFERROR(IF(K10="","",IF(J10&lt;&gt;"PASS","SKIP — illiquid",L10)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10">
-        <f>IF(N11="","",RANK(N11,$N$3:$N$27))</f>
+        <f>IF(K11="","",RANK(K11,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B11" s="25">
@@ -10719,42 +10602,30 @@
         <f>IFERROR(Bonds_Live!K11,"")</f>
         <v/>
       </c>
-      <c r="I11" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H32,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I32,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="36">
-        <f>IFERROR(Spread_History!H11,"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="34">
+      <c r="I11" s="34">
         <f>IFERROR(Liquidity_Gate!I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="25">
+      <c r="J11" s="25">
         <f>IFERROR(Liquidity_Gate!J11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="16">
-        <f>IFERROR(Settings!$C$42*((E11-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F11-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G11-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H11-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I11-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J11-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K11-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L11-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O11" s="10">
-        <f>IFERROR(IF(N11="","",IF(N11&gt;1,"STRONG BUY",IF(N11&gt;0.3,"BUY",IF(N11&gt;-0.3,"HOLD",IF(N11&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="10">
-        <f>IFERROR(IF(N11="","",IF(M11&lt;&gt;"PASS","SKIP — illiquid",O11)),"")</f>
+      <c r="K11" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E11),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F11),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G11),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H11),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I11),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E11-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F11-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G11-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H11-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I11-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E11),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F11),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G11),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H11),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I11),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="10">
+        <f>IFERROR(IF(K11="","",IF(K11&gt;1,"STRONG BUY",IF(K11&gt;0.3,"BUY",IF(K11&gt;-0.3,"HOLD",IF(K11&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="10">
+        <f>IFERROR(IF(K11="","",IF(J11&lt;&gt;"PASS","SKIP — illiquid",L11)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10">
-        <f>IF(N12="","",RANK(N12,$N$3:$N$27))</f>
+        <f>IF(K12="","",RANK(K12,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B12" s="25">
@@ -10785,42 +10656,30 @@
         <f>IFERROR(Bonds_Live!K12,"")</f>
         <v/>
       </c>
-      <c r="I12" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H33,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I33,"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="36">
-        <f>IFERROR(Spread_History!H12,"")</f>
-        <v/>
-      </c>
-      <c r="L12" s="34">
+      <c r="I12" s="34">
         <f>IFERROR(Liquidity_Gate!I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="J12" s="25">
         <f>IFERROR(Liquidity_Gate!J12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="16">
-        <f>IFERROR(Settings!$C$42*((E12-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F12-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G12-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H12-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I12-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J12-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K12-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L12-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>IFERROR(IF(N12="","",IF(N12&gt;1,"STRONG BUY",IF(N12&gt;0.3,"BUY",IF(N12&gt;-0.3,"HOLD",IF(N12&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P12" s="10">
-        <f>IFERROR(IF(N12="","",IF(M12&lt;&gt;"PASS","SKIP — illiquid",O12)),"")</f>
+      <c r="K12" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E12),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F12),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G12),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H12),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I12),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E12-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F12-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G12-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H12-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I12-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E12),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F12),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G12),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H12),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I12),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="10">
+        <f>IFERROR(IF(K12="","",IF(K12&gt;1,"STRONG BUY",IF(K12&gt;0.3,"BUY",IF(K12&gt;-0.3,"HOLD",IF(K12&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="10">
+        <f>IFERROR(IF(K12="","",IF(J12&lt;&gt;"PASS","SKIP — illiquid",L12)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10">
-        <f>IF(N13="","",RANK(N13,$N$3:$N$27))</f>
+        <f>IF(K13="","",RANK(K13,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B13" s="25">
@@ -10851,42 +10710,30 @@
         <f>IFERROR(Bonds_Live!K13,"")</f>
         <v/>
       </c>
-      <c r="I13" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H34,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I34,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="36">
-        <f>IFERROR(Spread_History!H13,"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="34">
+      <c r="I13" s="34">
         <f>IFERROR(Liquidity_Gate!I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="25">
+      <c r="J13" s="25">
         <f>IFERROR(Liquidity_Gate!J13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="16">
-        <f>IFERROR(Settings!$C$42*((E13-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F13-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G13-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H13-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I13-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J13-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K13-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L13-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O13" s="10">
-        <f>IFERROR(IF(N13="","",IF(N13&gt;1,"STRONG BUY",IF(N13&gt;0.3,"BUY",IF(N13&gt;-0.3,"HOLD",IF(N13&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="10">
-        <f>IFERROR(IF(N13="","",IF(M13&lt;&gt;"PASS","SKIP — illiquid",O13)),"")</f>
+      <c r="K13" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E13),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F13),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G13),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H13),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I13),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E13-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F13-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G13-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H13-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I13-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E13),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F13),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G13),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H13),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I13),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="10">
+        <f>IFERROR(IF(K13="","",IF(K13&gt;1,"STRONG BUY",IF(K13&gt;0.3,"BUY",IF(K13&gt;-0.3,"HOLD",IF(K13&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="10">
+        <f>IFERROR(IF(K13="","",IF(J13&lt;&gt;"PASS","SKIP — illiquid",L13)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10">
-        <f>IF(N14="","",RANK(N14,$N$3:$N$27))</f>
+        <f>IF(K14="","",RANK(K14,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B14" s="25">
@@ -10917,42 +10764,30 @@
         <f>IFERROR(Bonds_Live!K14,"")</f>
         <v/>
       </c>
-      <c r="I14" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H35,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I35,"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="36">
-        <f>IFERROR(Spread_History!H14,"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="34">
+      <c r="I14" s="34">
         <f>IFERROR(Liquidity_Gate!I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="25">
+      <c r="J14" s="25">
         <f>IFERROR(Liquidity_Gate!J14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="16">
-        <f>IFERROR(Settings!$C$42*((E14-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F14-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G14-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H14-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I14-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J14-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K14-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L14-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O14" s="10">
-        <f>IFERROR(IF(N14="","",IF(N14&gt;1,"STRONG BUY",IF(N14&gt;0.3,"BUY",IF(N14&gt;-0.3,"HOLD",IF(N14&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P14" s="10">
-        <f>IFERROR(IF(N14="","",IF(M14&lt;&gt;"PASS","SKIP — illiquid",O14)),"")</f>
+      <c r="K14" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E14),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F14),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G14),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H14),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I14),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E14-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F14-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G14-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H14-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I14-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E14),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F14),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G14),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H14),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I14),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="10">
+        <f>IFERROR(IF(K14="","",IF(K14&gt;1,"STRONG BUY",IF(K14&gt;0.3,"BUY",IF(K14&gt;-0.3,"HOLD",IF(K14&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="10">
+        <f>IFERROR(IF(K14="","",IF(J14&lt;&gt;"PASS","SKIP — illiquid",L14)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10">
-        <f>IF(N15="","",RANK(N15,$N$3:$N$27))</f>
+        <f>IF(K15="","",RANK(K15,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B15" s="25">
@@ -10983,42 +10818,30 @@
         <f>IFERROR(Bonds_Live!K15,"")</f>
         <v/>
       </c>
-      <c r="I15" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H36,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I36,"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="36">
-        <f>IFERROR(Spread_History!H15,"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="34">
+      <c r="I15" s="34">
         <f>IFERROR(Liquidity_Gate!I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="25">
+      <c r="J15" s="25">
         <f>IFERROR(Liquidity_Gate!J15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="16">
-        <f>IFERROR(Settings!$C$42*((E15-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F15-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G15-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H15-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I15-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J15-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K15-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L15-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O15" s="10">
-        <f>IFERROR(IF(N15="","",IF(N15&gt;1,"STRONG BUY",IF(N15&gt;0.3,"BUY",IF(N15&gt;-0.3,"HOLD",IF(N15&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="10">
-        <f>IFERROR(IF(N15="","",IF(M15&lt;&gt;"PASS","SKIP — illiquid",O15)),"")</f>
+      <c r="K15" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E15),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F15),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G15),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H15),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I15),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E15-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F15-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G15-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H15-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I15-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E15),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F15),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G15),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H15),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I15),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="10">
+        <f>IFERROR(IF(K15="","",IF(K15&gt;1,"STRONG BUY",IF(K15&gt;0.3,"BUY",IF(K15&gt;-0.3,"HOLD",IF(K15&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="10">
+        <f>IFERROR(IF(K15="","",IF(J15&lt;&gt;"PASS","SKIP — illiquid",L15)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10">
-        <f>IF(N16="","",RANK(N16,$N$3:$N$27))</f>
+        <f>IF(K16="","",RANK(K16,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B16" s="25">
@@ -11049,42 +10872,30 @@
         <f>IFERROR(Bonds_Live!K16,"")</f>
         <v/>
       </c>
-      <c r="I16" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H37,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I37,"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="36">
-        <f>IFERROR(Spread_History!H16,"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="34">
+      <c r="I16" s="34">
         <f>IFERROR(Liquidity_Gate!I16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="J16" s="25">
         <f>IFERROR(Liquidity_Gate!J16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="16">
-        <f>IFERROR(Settings!$C$42*((E16-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F16-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G16-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H16-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I16-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J16-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K16-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L16-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O16" s="10">
-        <f>IFERROR(IF(N16="","",IF(N16&gt;1,"STRONG BUY",IF(N16&gt;0.3,"BUY",IF(N16&gt;-0.3,"HOLD",IF(N16&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="10">
-        <f>IFERROR(IF(N16="","",IF(M16&lt;&gt;"PASS","SKIP — illiquid",O16)),"")</f>
+      <c r="K16" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E16),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F16),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G16),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H16),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I16),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E16-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F16-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G16-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H16-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I16-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E16),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F16),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G16),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H16),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I16),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="10">
+        <f>IFERROR(IF(K16="","",IF(K16&gt;1,"STRONG BUY",IF(K16&gt;0.3,"BUY",IF(K16&gt;-0.3,"HOLD",IF(K16&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="10">
+        <f>IFERROR(IF(K16="","",IF(J16&lt;&gt;"PASS","SKIP — illiquid",L16)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10">
-        <f>IF(N17="","",RANK(N17,$N$3:$N$27))</f>
+        <f>IF(K17="","",RANK(K17,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B17" s="25">
@@ -11115,42 +10926,30 @@
         <f>IFERROR(Bonds_Live!K17,"")</f>
         <v/>
       </c>
-      <c r="I17" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H38,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I38,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="36">
-        <f>IFERROR(Spread_History!H17,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="34">
+      <c r="I17" s="34">
         <f>IFERROR(Liquidity_Gate!I17,"")</f>
         <v/>
       </c>
-      <c r="M17" s="25">
+      <c r="J17" s="25">
         <f>IFERROR(Liquidity_Gate!J17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="16">
-        <f>IFERROR(Settings!$C$42*((E17-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F17-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G17-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H17-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I17-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J17-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K17-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L17-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O17" s="10">
-        <f>IFERROR(IF(N17="","",IF(N17&gt;1,"STRONG BUY",IF(N17&gt;0.3,"BUY",IF(N17&gt;-0.3,"HOLD",IF(N17&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="10">
-        <f>IFERROR(IF(N17="","",IF(M17&lt;&gt;"PASS","SKIP — illiquid",O17)),"")</f>
+      <c r="K17" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E17),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F17),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G17),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H17),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I17),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E17-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F17-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G17-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H17-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I17-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E17),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F17),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G17),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H17),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I17),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="10">
+        <f>IFERROR(IF(K17="","",IF(K17&gt;1,"STRONG BUY",IF(K17&gt;0.3,"BUY",IF(K17&gt;-0.3,"HOLD",IF(K17&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="10">
+        <f>IFERROR(IF(K17="","",IF(J17&lt;&gt;"PASS","SKIP — illiquid",L17)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10">
-        <f>IF(N18="","",RANK(N18,$N$3:$N$27))</f>
+        <f>IF(K18="","",RANK(K18,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B18" s="25">
@@ -11181,42 +10980,30 @@
         <f>IFERROR(Bonds_Live!K18,"")</f>
         <v/>
       </c>
-      <c r="I18" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H39,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I39,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="36">
-        <f>IFERROR(Spread_History!H18,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="34">
+      <c r="I18" s="34">
         <f>IFERROR(Liquidity_Gate!I18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="25">
+      <c r="J18" s="25">
         <f>IFERROR(Liquidity_Gate!J18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="16">
-        <f>IFERROR(Settings!$C$42*((E18-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F18-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G18-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H18-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I18-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J18-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K18-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L18-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O18" s="10">
-        <f>IFERROR(IF(N18="","",IF(N18&gt;1,"STRONG BUY",IF(N18&gt;0.3,"BUY",IF(N18&gt;-0.3,"HOLD",IF(N18&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P18" s="10">
-        <f>IFERROR(IF(N18="","",IF(M18&lt;&gt;"PASS","SKIP — illiquid",O18)),"")</f>
+      <c r="K18" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E18),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F18),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G18),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H18),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I18),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E18-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F18-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G18-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H18-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I18-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E18),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F18),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G18),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H18),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I18),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="10">
+        <f>IFERROR(IF(K18="","",IF(K18&gt;1,"STRONG BUY",IF(K18&gt;0.3,"BUY",IF(K18&gt;-0.3,"HOLD",IF(K18&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="10">
+        <f>IFERROR(IF(K18="","",IF(J18&lt;&gt;"PASS","SKIP — illiquid",L18)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10">
-        <f>IF(N19="","",RANK(N19,$N$3:$N$27))</f>
+        <f>IF(K19="","",RANK(K19,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B19" s="25">
@@ -11247,42 +11034,30 @@
         <f>IFERROR(Bonds_Live!K19,"")</f>
         <v/>
       </c>
-      <c r="I19" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H40,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I40,"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="36">
-        <f>IFERROR(Spread_History!H19,"")</f>
-        <v/>
-      </c>
-      <c r="L19" s="34">
+      <c r="I19" s="34">
         <f>IFERROR(Liquidity_Gate!I19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="25">
+      <c r="J19" s="25">
         <f>IFERROR(Liquidity_Gate!J19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="16">
-        <f>IFERROR(Settings!$C$42*((E19-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F19-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G19-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H19-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I19-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J19-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K19-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L19-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O19" s="10">
-        <f>IFERROR(IF(N19="","",IF(N19&gt;1,"STRONG BUY",IF(N19&gt;0.3,"BUY",IF(N19&gt;-0.3,"HOLD",IF(N19&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P19" s="10">
-        <f>IFERROR(IF(N19="","",IF(M19&lt;&gt;"PASS","SKIP — illiquid",O19)),"")</f>
+      <c r="K19" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E19),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F19),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G19),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H19),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I19),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E19-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F19-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G19-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H19-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I19-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E19),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F19),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G19),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H19),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I19),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="10">
+        <f>IFERROR(IF(K19="","",IF(K19&gt;1,"STRONG BUY",IF(K19&gt;0.3,"BUY",IF(K19&gt;-0.3,"HOLD",IF(K19&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="10">
+        <f>IFERROR(IF(K19="","",IF(J19&lt;&gt;"PASS","SKIP — illiquid",L19)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10">
-        <f>IF(N20="","",RANK(N20,$N$3:$N$27))</f>
+        <f>IF(K20="","",RANK(K20,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B20" s="25">
@@ -11313,42 +11088,30 @@
         <f>IFERROR(Bonds_Live!K20,"")</f>
         <v/>
       </c>
-      <c r="I20" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H41,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I41,"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="36">
-        <f>IFERROR(Spread_History!H20,"")</f>
-        <v/>
-      </c>
-      <c r="L20" s="34">
+      <c r="I20" s="34">
         <f>IFERROR(Liquidity_Gate!I20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="25">
+      <c r="J20" s="25">
         <f>IFERROR(Liquidity_Gate!J20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="16">
-        <f>IFERROR(Settings!$C$42*((E20-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F20-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G20-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H20-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I20-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J20-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K20-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L20-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O20" s="10">
-        <f>IFERROR(IF(N20="","",IF(N20&gt;1,"STRONG BUY",IF(N20&gt;0.3,"BUY",IF(N20&gt;-0.3,"HOLD",IF(N20&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P20" s="10">
-        <f>IFERROR(IF(N20="","",IF(M20&lt;&gt;"PASS","SKIP — illiquid",O20)),"")</f>
+      <c r="K20" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E20),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F20),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G20),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H20),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I20),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E20-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F20-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G20-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H20-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I20-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E20),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F20),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G20),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H20),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I20),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="10">
+        <f>IFERROR(IF(K20="","",IF(K20&gt;1,"STRONG BUY",IF(K20&gt;0.3,"BUY",IF(K20&gt;-0.3,"HOLD",IF(K20&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="10">
+        <f>IFERROR(IF(K20="","",IF(J20&lt;&gt;"PASS","SKIP — illiquid",L20)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10">
-        <f>IF(N21="","",RANK(N21,$N$3:$N$27))</f>
+        <f>IF(K21="","",RANK(K21,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B21" s="25">
@@ -11379,42 +11142,30 @@
         <f>IFERROR(Bonds_Live!K21,"")</f>
         <v/>
       </c>
-      <c r="I21" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H42,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I42,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="36">
-        <f>IFERROR(Spread_History!H21,"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="34">
+      <c r="I21" s="34">
         <f>IFERROR(Liquidity_Gate!I21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="25">
+      <c r="J21" s="25">
         <f>IFERROR(Liquidity_Gate!J21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="16">
-        <f>IFERROR(Settings!$C$42*((E21-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F21-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G21-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H21-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I21-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J21-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K21-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L21-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O21" s="10">
-        <f>IFERROR(IF(N21="","",IF(N21&gt;1,"STRONG BUY",IF(N21&gt;0.3,"BUY",IF(N21&gt;-0.3,"HOLD",IF(N21&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="10">
-        <f>IFERROR(IF(N21="","",IF(M21&lt;&gt;"PASS","SKIP — illiquid",O21)),"")</f>
+      <c r="K21" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E21),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F21),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G21),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H21),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I21),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E21-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F21-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G21-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H21-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I21-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E21),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F21),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G21),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H21),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I21),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="10">
+        <f>IFERROR(IF(K21="","",IF(K21&gt;1,"STRONG BUY",IF(K21&gt;0.3,"BUY",IF(K21&gt;-0.3,"HOLD",IF(K21&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
+        <f>IFERROR(IF(K21="","",IF(J21&lt;&gt;"PASS","SKIP — illiquid",L21)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10">
-        <f>IF(N22="","",RANK(N22,$N$3:$N$27))</f>
+        <f>IF(K22="","",RANK(K22,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B22" s="25">
@@ -11445,42 +11196,30 @@
         <f>IFERROR(Bonds_Live!K22,"")</f>
         <v/>
       </c>
-      <c r="I22" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H43,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I43,"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="36">
-        <f>IFERROR(Spread_History!H22,"")</f>
-        <v/>
-      </c>
-      <c r="L22" s="34">
+      <c r="I22" s="34">
         <f>IFERROR(Liquidity_Gate!I22,"")</f>
         <v/>
       </c>
-      <c r="M22" s="25">
+      <c r="J22" s="25">
         <f>IFERROR(Liquidity_Gate!J22,"")</f>
         <v/>
       </c>
-      <c r="N22" s="16">
-        <f>IFERROR(Settings!$C$42*((E22-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F22-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G22-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H22-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I22-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J22-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K22-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L22-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O22" s="10">
-        <f>IFERROR(IF(N22="","",IF(N22&gt;1,"STRONG BUY",IF(N22&gt;0.3,"BUY",IF(N22&gt;-0.3,"HOLD",IF(N22&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P22" s="10">
-        <f>IFERROR(IF(N22="","",IF(M22&lt;&gt;"PASS","SKIP — illiquid",O22)),"")</f>
+      <c r="K22" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E22),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F22),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G22),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H22),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I22),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E22-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F22-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G22-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H22-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I22-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E22),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F22),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G22),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H22),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I22),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="10">
+        <f>IFERROR(IF(K22="","",IF(K22&gt;1,"STRONG BUY",IF(K22&gt;0.3,"BUY",IF(K22&gt;-0.3,"HOLD",IF(K22&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="10">
+        <f>IFERROR(IF(K22="","",IF(J22&lt;&gt;"PASS","SKIP — illiquid",L22)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10">
-        <f>IF(N23="","",RANK(N23,$N$3:$N$27))</f>
+        <f>IF(K23="","",RANK(K23,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B23" s="25">
@@ -11511,42 +11250,30 @@
         <f>IFERROR(Bonds_Live!K23,"")</f>
         <v/>
       </c>
-      <c r="I23" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H44,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I44,"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="36">
-        <f>IFERROR(Spread_History!H23,"")</f>
-        <v/>
-      </c>
-      <c r="L23" s="34">
+      <c r="I23" s="34">
         <f>IFERROR(Liquidity_Gate!I23,"")</f>
         <v/>
       </c>
-      <c r="M23" s="25">
+      <c r="J23" s="25">
         <f>IFERROR(Liquidity_Gate!J23,"")</f>
         <v/>
       </c>
-      <c r="N23" s="16">
-        <f>IFERROR(Settings!$C$42*((E23-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F23-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G23-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H23-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I23-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J23-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K23-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L23-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O23" s="10">
-        <f>IFERROR(IF(N23="","",IF(N23&gt;1,"STRONG BUY",IF(N23&gt;0.3,"BUY",IF(N23&gt;-0.3,"HOLD",IF(N23&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P23" s="10">
-        <f>IFERROR(IF(N23="","",IF(M23&lt;&gt;"PASS","SKIP — illiquid",O23)),"")</f>
+      <c r="K23" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E23),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F23),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G23),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H23),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I23),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E23-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F23-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G23-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H23-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I23-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E23),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F23),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G23),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H23),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I23),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="10">
+        <f>IFERROR(IF(K23="","",IF(K23&gt;1,"STRONG BUY",IF(K23&gt;0.3,"BUY",IF(K23&gt;-0.3,"HOLD",IF(K23&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="10">
+        <f>IFERROR(IF(K23="","",IF(J23&lt;&gt;"PASS","SKIP — illiquid",L23)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10">
-        <f>IF(N24="","",RANK(N24,$N$3:$N$27))</f>
+        <f>IF(K24="","",RANK(K24,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B24" s="25">
@@ -11577,42 +11304,30 @@
         <f>IFERROR(Bonds_Live!K24,"")</f>
         <v/>
       </c>
-      <c r="I24" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H45,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I45,"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="36">
-        <f>IFERROR(Spread_History!H24,"")</f>
-        <v/>
-      </c>
-      <c r="L24" s="34">
+      <c r="I24" s="34">
         <f>IFERROR(Liquidity_Gate!I24,"")</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="J24" s="25">
         <f>IFERROR(Liquidity_Gate!J24,"")</f>
         <v/>
       </c>
-      <c r="N24" s="16">
-        <f>IFERROR(Settings!$C$42*((E24-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F24-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G24-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H24-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I24-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J24-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K24-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L24-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O24" s="10">
-        <f>IFERROR(IF(N24="","",IF(N24&gt;1,"STRONG BUY",IF(N24&gt;0.3,"BUY",IF(N24&gt;-0.3,"HOLD",IF(N24&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P24" s="10">
-        <f>IFERROR(IF(N24="","",IF(M24&lt;&gt;"PASS","SKIP — illiquid",O24)),"")</f>
+      <c r="K24" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E24),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F24),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G24),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H24),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I24),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E24-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F24-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G24-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H24-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I24-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E24),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F24),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G24),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H24),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I24),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="10">
+        <f>IFERROR(IF(K24="","",IF(K24&gt;1,"STRONG BUY",IF(K24&gt;0.3,"BUY",IF(K24&gt;-0.3,"HOLD",IF(K24&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="10">
+        <f>IFERROR(IF(K24="","",IF(J24&lt;&gt;"PASS","SKIP — illiquid",L24)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10">
-        <f>IF(N25="","",RANK(N25,$N$3:$N$27))</f>
+        <f>IF(K25="","",RANK(K25,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B25" s="25">
@@ -11643,42 +11358,30 @@
         <f>IFERROR(Bonds_Live!K25,"")</f>
         <v/>
       </c>
-      <c r="I25" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H46,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I46,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="36">
-        <f>IFERROR(Spread_History!H25,"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="34">
+      <c r="I25" s="34">
         <f>IFERROR(Liquidity_Gate!I25,"")</f>
         <v/>
       </c>
-      <c r="M25" s="25">
+      <c r="J25" s="25">
         <f>IFERROR(Liquidity_Gate!J25,"")</f>
         <v/>
       </c>
-      <c r="N25" s="16">
-        <f>IFERROR(Settings!$C$42*((E25-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F25-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G25-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H25-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I25-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J25-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K25-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L25-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O25" s="10">
-        <f>IFERROR(IF(N25="","",IF(N25&gt;1,"STRONG BUY",IF(N25&gt;0.3,"BUY",IF(N25&gt;-0.3,"HOLD",IF(N25&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P25" s="10">
-        <f>IFERROR(IF(N25="","",IF(M25&lt;&gt;"PASS","SKIP — illiquid",O25)),"")</f>
+      <c r="K25" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E25),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F25),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G25),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H25),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I25),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E25-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F25-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G25-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H25-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I25-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E25),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F25),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G25),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H25),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I25),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="10">
+        <f>IFERROR(IF(K25="","",IF(K25&gt;1,"STRONG BUY",IF(K25&gt;0.3,"BUY",IF(K25&gt;-0.3,"HOLD",IF(K25&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="10">
+        <f>IFERROR(IF(K25="","",IF(J25&lt;&gt;"PASS","SKIP — illiquid",L25)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10">
-        <f>IF(N26="","",RANK(N26,$N$3:$N$27))</f>
+        <f>IF(K26="","",RANK(K26,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B26" s="25">
@@ -11709,42 +11412,30 @@
         <f>IFERROR(Bonds_Live!K26,"")</f>
         <v/>
       </c>
-      <c r="I26" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H47,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I47,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="36">
-        <f>IFERROR(Spread_History!H26,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="34">
+      <c r="I26" s="34">
         <f>IFERROR(Liquidity_Gate!I26,"")</f>
         <v/>
       </c>
-      <c r="M26" s="25">
+      <c r="J26" s="25">
         <f>IFERROR(Liquidity_Gate!J26,"")</f>
         <v/>
       </c>
-      <c r="N26" s="16">
-        <f>IFERROR(Settings!$C$42*((E26-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F26-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G26-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H26-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I26-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J26-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K26-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L26-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O26" s="10">
-        <f>IFERROR(IF(N26="","",IF(N26&gt;1,"STRONG BUY",IF(N26&gt;0.3,"BUY",IF(N26&gt;-0.3,"HOLD",IF(N26&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="10">
-        <f>IFERROR(IF(N26="","",IF(M26&lt;&gt;"PASS","SKIP — illiquid",O26)),"")</f>
+      <c r="K26" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E26),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F26),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G26),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H26),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I26),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E26-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F26-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G26-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H26-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I26-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E26),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F26),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G26),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H26),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I26),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="10">
+        <f>IFERROR(IF(K26="","",IF(K26&gt;1,"STRONG BUY",IF(K26&gt;0.3,"BUY",IF(K26&gt;-0.3,"HOLD",IF(K26&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="10">
+        <f>IFERROR(IF(K26="","",IF(J26&lt;&gt;"PASS","SKIP — illiquid",L26)),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10">
-        <f>IF(N27="","",RANK(N27,$N$3:$N$27))</f>
+        <f>IF(K27="","",RANK(K27,$K$3:$K$27))</f>
         <v/>
       </c>
       <c r="B27" s="25">
@@ -11775,41 +11466,29 @@
         <f>IFERROR(Bonds_Live!K27,"")</f>
         <v/>
       </c>
-      <c r="I27" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!H48,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="36">
-        <f>IFERROR(Peer_EMBI_Bench!I48,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="36">
-        <f>IFERROR(Spread_History!H27,"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="34">
+      <c r="I27" s="34">
         <f>IFERROR(Liquidity_Gate!I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="25">
+      <c r="J27" s="25">
         <f>IFERROR(Liquidity_Gate!J27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="16">
-        <f>IFERROR(Settings!$C$42*((E27-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27))+Settings!$C$43*((F27-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27))+Settings!$C$44*((G27-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27))+Settings!$C$45*((H27-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27))+Settings!$C$46*((I27-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27))+Settings!$C$47*((J27-AVERAGE($J$3:$J$27))/STDEV($J$3:$J$27))+Settings!$C$48*((K27-AVERAGE($K$3:$K$27))/STDEV($K$3:$K$27))+Settings!$C$49*((L27-AVERAGE($L$3:$L$27))/STDEV($L$3:$L$27)),"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="10">
-        <f>IFERROR(IF(N27="","",IF(N27&gt;1,"STRONG BUY",IF(N27&gt;0.3,"BUY",IF(N27&gt;-0.3,"HOLD",IF(N27&gt;-1,"SELL","STRONG SELL"))))),"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="10">
-        <f>IFERROR(IF(N27="","",IF(M27&lt;&gt;"PASS","SKIP — illiquid",O27)),"")</f>
+      <c r="K27" s="16">
+        <f>IFERROR(IF((IFERROR(IF(AND(ISNUMBER(E27),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F27),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G27),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H27),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I27),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))=0,"",(IFERROR(Settings!$C$42*((E27-AVERAGE($E$3:$E$27))/STDEV($E$3:$E$27)),0)+IFERROR(Settings!$C$43*((F27-AVERAGE($F$3:$F$27))/STDEV($F$3:$F$27)),0)+IFERROR(Settings!$C$44*((G27-AVERAGE($G$3:$G$27))/STDEV($G$3:$G$27)),0)+IFERROR(Settings!$C$45*((H27-AVERAGE($H$3:$H$27))/STDEV($H$3:$H$27)),0)+IFERROR(Settings!$C$46*((I27-AVERAGE($I$3:$I$27))/STDEV($I$3:$I$27)),0))/(IFERROR(IF(AND(ISNUMBER(E27),STDEV($E$3:$E$27)&gt;0),Settings!$C$42,0),0)+IFERROR(IF(AND(ISNUMBER(F27),STDEV($F$3:$F$27)&gt;0),Settings!$C$43,0),0)+IFERROR(IF(AND(ISNUMBER(G27),STDEV($G$3:$G$27)&gt;0),Settings!$C$44,0),0)+IFERROR(IF(AND(ISNUMBER(H27),STDEV($H$3:$H$27)&gt;0),Settings!$C$45,0),0)+IFERROR(IF(AND(ISNUMBER(I27),STDEV($I$3:$I$27)&gt;0),Settings!$C$46,0),0))),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="10">
+        <f>IFERROR(IF(K27="","",IF(K27&gt;1,"STRONG BUY",IF(K27&gt;0.3,"BUY",IF(K27&gt;-0.3,"HOLD",IF(K27&gt;-1,"SELL","STRONG SELL"))))),"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="10">
+        <f>IFERROR(IF(K27="","",IF(J27&lt;&gt;"PASS","SKIP — illiquid",L27)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N3:N27">
+  <conditionalFormatting sqref="K3:K27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11962,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M8,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M8,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -11998,11 +11677,11 @@
         <v/>
       </c>
       <c r="L8" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C8,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C8,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M8" s="16">
-        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),1),"")</f>
+        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),1),"")</f>
         <v/>
       </c>
       <c r="N8" s="38">
@@ -12019,7 +11698,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M9,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M9,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -12055,11 +11734,11 @@
         <v/>
       </c>
       <c r="L9" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C9,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C9,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M9" s="16">
-        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),2),"")</f>
+        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),2),"")</f>
         <v/>
       </c>
       <c r="N9" s="38">
@@ -12076,7 +11755,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M10,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M10,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
@@ -12112,11 +11791,11 @@
         <v/>
       </c>
       <c r="L10" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C10,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C10,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M10" s="16">
-        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),3),"")</f>
+        <f>IFERROR(LARGE(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),3),"")</f>
         <v/>
       </c>
       <c r="N10" s="38">
@@ -12225,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M14,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M14,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="10">
@@ -12261,11 +11940,11 @@
         <v/>
       </c>
       <c r="L14" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C14,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C14,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M14" s="16">
-        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),1),"")</f>
+        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),1),"")</f>
         <v/>
       </c>
       <c r="N14" s="38">
@@ -12282,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M15,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M15,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="10">
@@ -12318,11 +11997,11 @@
         <v/>
       </c>
       <c r="L15" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C15,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C15,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M15" s="16">
-        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),2),"")</f>
+        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),2),"")</f>
         <v/>
       </c>
       <c r="N15" s="38">
@@ -12339,7 +12018,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M16,Rich_Cheap_Rank!N$3:N$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!B$3:B$27,MATCH(M16,Rich_Cheap_Rank!K$3:K$27,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="10">
@@ -12375,11 +12054,11 @@
         <v/>
       </c>
       <c r="L16" s="10">
-        <f>IFERROR(INDEX(Rich_Cheap_Rank!P$3:P$27,MATCH($C16,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
+        <f>IFERROR(INDEX(Rich_Cheap_Rank!M$3:M$27,MATCH($C16,Rich_Cheap_Rank!B$3:B$27,0)),"")</f>
         <v/>
       </c>
       <c r="M16" s="16">
-        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!M$3:M$27="PASS",Rich_Cheap_Rank!N$3:N$27),3),"")</f>
+        <f>IFERROR(SMALL(IF(Rich_Cheap_Rank!J$3:J$27="PASS",Rich_Cheap_Rank!K$3:K$27),3),"")</f>
         <v/>
       </c>
       <c r="N16" s="38">
@@ -13043,7 +12722,12 @@
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Composite uses 5 intrinsic signals only. Peer / EMBI / 1Y-percentile tabs remain as standalone diagnostics. If a bond is missing data on a signal, that signal's weight is automatically removed from BOTH numerator and denominator — you always get a composite z, just based on whichever signals are available.</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -13053,7 +12737,7 @@
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -13063,7 +12747,7 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -13073,57 +12757,27 @@
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Spread vs peer basket</t>
+          <t>Liquidity score (boost)</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>Spread vs EMBI bucket</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>1Y spread percentile (high = +)</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Liquidity score (boost)</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Sum (should = 100%)</t>
         </is>
       </c>
-      <c r="C50" s="20">
-        <f>SUM(C42:C49)</f>
+      <c r="C47" s="20">
+        <f>SUM(C42:C46)</f>
         <v/>
       </c>
     </row>
@@ -13193,7 +12847,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="E12:E17"/>
@@ -13202,6 +12856,7 @@
     <mergeCell ref="E28:E31"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="E42:E46"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="E53:E57"/>
   </mergeCells>
